--- a/tests/fixtures/salesforce_olympia_sample.xlsx
+++ b/tests/fixtures/salesforce_olympia_sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GM SOP" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,480 +416,497 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A2:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Sub Status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Job Number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Contact Full Name</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Opportunity Name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Next Step-WO</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Days in Current Sub Status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Close Date</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Sales Rep 1 Name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Sales Rep 2 Name</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Olympia</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Item Notification</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Roofing</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>273140</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Ivan Sanchez</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>8409 Spruce Street Southwest Lakewood Washington 98498</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>08/13 FU MB 08/10 Need PO for whole roof, need plywood diagram MB</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>29598.91</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Leona Miles</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Nolen Moore</t>
+          <t>GM SOP</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Roofing</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>274803</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Robert Gillis</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>13027 Kapowsin Highlands Dr E Graham Washington 98338</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>08/13 FU. CB. 08/12 FU. CB. 08/11 FU CB. Sent email on approval.</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>15475</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46256</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Jose Perez</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Jorge Sande</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Siding</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>274000</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Tom Randles</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>9949 Beth Court Southeast Yelm Washington 98597</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>08/12 Need HO to confirm new color or siding type and hover re-built.</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>71417.91</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Dale Porter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>116491.82</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>As of 2026-08-13 14:00:09 Pacific Standard Time/PST • Sorted by Close Date (Descending)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Install Issue</t>
+          <t>Filtered By</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>275101</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Erin Walsh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>4207 Cooper Point Road Olympia Washington 98502</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Confirm replacement sash delivery and installer availability.</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>18750</v>
-      </c>
-      <c r="I7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Leona Miles</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Nolen Moore</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Show: All opportunities</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Roofing</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>275112</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Paul Young</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1700 East Bay Drive Northeast Olympia Washington 98506</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Verify flashing correction photos before closeout.</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>24200</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>46255</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Jose Perez</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Status not equal to Cancel Outside Recission,Canceled,Completed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
+          <t>Service Project equals False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Market  ↑</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sub Status  ↓</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Product  ↑</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Job Number</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Contact: Full Name</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Opportunity Name</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Next Step-WO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Days in Current Sub Status</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Close Date</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Assigned Service Resource: Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Olympia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Item Notification</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Roofing</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>273140</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ivan Sanchez</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8409 Spruce Street Southwest Lakewood Washington 98498</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>08/13 FU MB 08/10 Need PO for whole roof, need plywood diagram MB</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>29598.91</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Roofing</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>274803</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Robert Gillis</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>13027 Kapowsin Highlands Dr E Graham Washington 98338</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>08/13 FU. CB. 08/12 FU. CB. 08/11 FU CB. Sent email on approval.</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>15475</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Jose Perez</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Siding</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>274000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tom Randles</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>9949 Beth Court Southeast Yelm Washington 98597</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>08/12 Need HO to confirm new color or siding type and hover re-built.</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>71417.91</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Dale Porter</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I15" t="n">
+        <v>116491.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Install Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Windows</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>275101</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Erin Walsh</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4207 Cooper Point Road Olympia Washington 98502</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Confirm replacement sash delivery and installer availability.</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>18750</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Roofing</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>275112</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Paul Young</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1700 East Bay Drive Northeast Olympia Washington 98506</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Verify flashing correction photos before closeout.</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>24200</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Jose Perez</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>42950</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
+    <row r="20">
+      <c r="C20" t="inlineStr">
         <is>
           <t>On Hold</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
+    <row r="21">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Siding</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>275150</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Maria Lee</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>510 Capitol Way South Olympia Washington 98501</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Waiting for HOA color authorization.</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I21" t="n">
         <v>32800</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J21" t="n">
         <v>12</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Dale Porter</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Jorge Sande</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Tacoma</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Item Notification</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Roofing</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>900001</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Not Olympia One</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Tacoma Washington</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>This row must be filtered out.</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I22" t="n">
         <v>99000</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J22" t="n">
         <v>20</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>46267</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Other Rep</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" t="inlineStr">
+    <row r="23">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Roofing</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>900002</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Not Olympia Two</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Tacoma Washington</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Fill-down must keep this row in Tacoma and filter it out.</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I23" t="n">
         <v>88000</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J23" t="n">
         <v>19</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Other Rep</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I24" t="n">
         <v>379241.82</v>
       </c>
     </row>

--- a/tests/fixtures/salesforce_olympia_sample.xlsx
+++ b/tests/fixtures/salesforce_olympia_sample.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M24"/>
+  <dimension ref="A2:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -517,6 +517,16 @@
           <t>Assigned Service Resource: Name</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Sales Rep 1 Name</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Sales Rep 2 Name</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -568,6 +578,16 @@
           <t>Leona Miles</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="D13" t="inlineStr">
@@ -609,6 +629,16 @@
           <t>Jose Perez</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Jose Perez</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Jorge Sande</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="D14" t="inlineStr">
@@ -650,6 +680,16 @@
           <t>Dale Porter</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Dale Porter</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="C15" t="inlineStr">
@@ -660,6 +700,16 @@
       <c r="I15" t="n">
         <v>116491.82</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Erin Walsh</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="inlineStr">
@@ -667,6 +717,16 @@
           <t>Install Issue</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="D17" t="inlineStr">
@@ -708,6 +768,16 @@
           <t>Leona Miles</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Jose Perez</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Jorge Sande</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="D18" t="inlineStr">
@@ -749,6 +819,16 @@
           <t>Jose Perez</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Dale Porter</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
@@ -759,6 +839,16 @@
       <c r="I19" t="n">
         <v>42950</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Erin Walsh</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
@@ -766,6 +856,16 @@
           <t>On Hold</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="D21" t="inlineStr">
@@ -807,6 +907,16 @@
           <t>Dale Porter</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Jose Perez</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jorge Sande</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -858,6 +968,16 @@
           <t>Other Rep</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Dale Porter</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ana Ruiz</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="D23" t="inlineStr">
@@ -899,6 +1019,16 @@
           <t>Other Rep</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Erin Walsh</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -908,6 +1038,16 @@
       </c>
       <c r="I24" t="n">
         <v>379241.82</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Leona Miles</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Nolen Moore</t>
+        </is>
       </c>
     </row>
   </sheetData>
